--- a/CNA01D.xlsx
+++ b/CNA01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="99">
   <si>
     <t/>
   </si>
@@ -82,42 +82,12 @@
     <t>IDM CD WNT 2'S L/XL</t>
   </si>
   <si>
-    <t>20122827</t>
-  </si>
-  <si>
-    <t>GT MAN BOXER XL(NEW)</t>
-  </si>
-  <si>
     <t>20140419</t>
   </si>
   <si>
     <t>IDM CD WNT SOFT 2-XL</t>
   </si>
   <si>
-    <t>20122826</t>
-  </si>
-  <si>
-    <t>GT MAN BOXER M (NEW)</t>
-  </si>
-  <si>
-    <t>20038558</t>
-  </si>
-  <si>
-    <t>GTMAN CD GTH 2'S L</t>
-  </si>
-  <si>
-    <t>20038559</t>
-  </si>
-  <si>
-    <t>GTMAN CD GTH 2'S M</t>
-  </si>
-  <si>
-    <t>20065487</t>
-  </si>
-  <si>
-    <t>GTMAN CD GTH 2'S XL</t>
-  </si>
-  <si>
     <t>20025648</t>
   </si>
   <si>
@@ -130,24 +100,6 @@
     <t>GTMAN CD GTM01/2S XL</t>
   </si>
   <si>
-    <t>20009186</t>
-  </si>
-  <si>
-    <t>GT MAN CD GTVL 01/3L</t>
-  </si>
-  <si>
-    <t>20010257</t>
-  </si>
-  <si>
-    <t>GT MAN CD GTVL01/3XL</t>
-  </si>
-  <si>
-    <t>20010262</t>
-  </si>
-  <si>
-    <t>GT MAN CD 708 3'S/M</t>
-  </si>
-  <si>
     <t>20010263</t>
   </si>
   <si>
@@ -314,24 +266,6 @@
   </si>
   <si>
     <t>IDM CLMAX BRIEF XL2S</t>
-  </si>
-  <si>
-    <t>10002788</t>
-  </si>
-  <si>
-    <t>GT MAN CD 704BW-L</t>
-  </si>
-  <si>
-    <t>10002789</t>
-  </si>
-  <si>
-    <t>GT MAN CD 704BW-XL</t>
-  </si>
-  <si>
-    <t>20073868</t>
-  </si>
-  <si>
-    <t>GTMAN GTS01 PB-BL XL</t>
   </si>
   <si>
     <t>10039944</t>
@@ -766,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -953,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -967,13 +901,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -987,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>11</v>
@@ -1010,7 +944,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>15</v>
@@ -1030,7 +964,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>15</v>
@@ -1038,10 +972,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1050,7 +984,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>15</v>
@@ -1058,10 +992,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1070,27 +1004,27 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>15</v>
@@ -1098,19 +1032,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>15</v>
@@ -1118,19 +1052,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>15</v>
@@ -1138,19 +1072,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>15</v>
@@ -1158,16 +1092,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>18</v>
@@ -1178,19 +1112,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>15</v>
@@ -1198,19 +1132,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>15</v>
@@ -1227,13 +1161,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1247,13 +1181,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1267,13 +1201,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1287,13 +1221,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1307,13 +1241,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1327,13 +1261,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1347,67 +1281,67 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>4</v>
@@ -1418,16 +1352,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>4</v>
@@ -1438,16 +1372,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
@@ -1458,16 +1392,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>11</v>
@@ -1478,19 +1412,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1498,19 +1432,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1518,19 +1452,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1538,19 +1472,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1567,10 +1501,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1587,10 +1521,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1607,10 +1541,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1627,10 +1561,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1647,232 +1581,12 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F55" s="1" t="s">
         <v>5</v>
       </c>
     </row>
